--- a/artfynd/A 11326-2026 artfynd.xlsx
+++ b/artfynd/A 11326-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131901993</v>
       </c>
       <c r="B2" t="n">
-        <v>93121</v>
+        <v>93126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131901956</v>
       </c>
       <c r="B3" t="n">
-        <v>79265</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11326-2026 artfynd.xlsx
+++ b/artfynd/A 11326-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131901993</v>
       </c>
       <c r="B2" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131901956</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11326-2026 artfynd.xlsx
+++ b/artfynd/A 11326-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131901993</v>
       </c>
       <c r="B2" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131901956</v>
       </c>
       <c r="B3" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11326-2026 artfynd.xlsx
+++ b/artfynd/A 11326-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131901993</v>
       </c>
       <c r="B2" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131901956</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11326-2026 artfynd.xlsx
+++ b/artfynd/A 11326-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131901993</v>
       </c>
       <c r="B2" t="n">
-        <v>93136</v>
+        <v>93172</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131901956</v>
       </c>
       <c r="B3" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11326-2026 artfynd.xlsx
+++ b/artfynd/A 11326-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131901993</v>
       </c>
       <c r="B2" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131901956</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11326-2026 artfynd.xlsx
+++ b/artfynd/A 11326-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>131901993</v>
       </c>
       <c r="B2" t="n">
-        <v>93186</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -790,11 +790,11 @@
         <v>131901956</v>
       </c>
       <c r="B3" t="n">
-        <v>79319</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -891,6 +891,352 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131902149</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rölettjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>505320</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6677348</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131902070</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rölettjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>505320</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6677348</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131902214</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rölettjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>505226</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6677338</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
